--- a/data/trans_orig/IP19D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19D-Provincia-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>28689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57979</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75553</t>
+          <t>74303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>21411</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34494</t>
+          <t>34261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>44139</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47453</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>18964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30847</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>31933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18773</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>44503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58182</t>
+          <t>58237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,25%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31607</t>
+          <t>32108</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41753</t>
+          <t>41694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>14575</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>21645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37668</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23512</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41074</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31968</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>44975</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>64572</t>
+          <t>63875</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82888</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31744</t>
+          <t>31192</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57380</t>
+          <t>56791</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>52165</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>65471</t>
+          <t>65575</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>50199</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>61472</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>106504</t>
+          <t>107162</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>123587</t>
+          <t>124816</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>206710</t>
+          <t>207600</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>237423</t>
+          <t>237500</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>212105</t>
+          <t>211900</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>241785</t>
+          <t>241549</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>427332</t>
+          <t>427426</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>466782</t>
+          <t>469310</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>125367</t>
+          <t>124167</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>130696</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>207297</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>247002</t>
+          <t>248226</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23501</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35895</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6772,12 +6772,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45673</t>
+          <t>45630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26779</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38743</t>
+          <t>38005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40269</t>
+          <t>40266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58207</t>
+          <t>58823</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75126</t>
+          <t>75348</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7341,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35875</t>
+          <t>36263</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>435</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -7910,12 +7910,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>28486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29316</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55191</t>
+          <t>54595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -8023,12 +8023,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35019</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8221,12 +8221,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -8479,12 +8479,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41346</t>
+          <t>41698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8705,12 +8705,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38779</t>
+          <t>39421</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9274,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27305</t>
+          <t>26600</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41233</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -9617,12 +9617,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>32116</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43638</t>
+          <t>42955</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>61362</t>
+          <t>61553</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9843,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>29027</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>41753</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79834</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>56149</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>41084</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>73468</t>
+          <t>73271</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>92854</t>
+          <t>92400</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>44147</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>62605</t>
+          <t>63311</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -10755,12 +10755,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>157786</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>189593</t>
+          <t>187322</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>156736</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>189022</t>
+          <t>190107</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10805,12 +10805,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>323262</t>
+          <t>324611</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>367097</t>
+          <t>368551</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -10868,12 +10868,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>183591</t>
+          <t>182451</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>152466</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>184650</t>
+          <t>185693</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>315884</t>
+          <t>314041</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>359062</t>
+          <t>357370</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -11560,12 +11560,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22389</t>
+          <t>22726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11610,12 +11610,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41557</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11786,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -12129,12 +12129,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36158</t>
+          <t>36642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12179,12 +12179,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74102</t>
+          <t>73975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -12355,12 +12355,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47690</t>
+          <t>47490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -12698,12 +12698,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12713,12 +12713,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17724</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12748,12 +12748,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>25320</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12783,12 +12783,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12939,12 +12939,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12974,12 +12974,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>23991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -13267,12 +13267,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29816</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>41390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58891</t>
+          <t>58310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13352,12 +13352,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32093</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52096</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -13836,12 +13836,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13921,12 +13921,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -14062,12 +14062,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14077,12 +14077,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14147,12 +14147,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -14405,12 +14405,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26754</t>
+          <t>26579</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14440,12 +14440,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14490,12 +14490,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -14631,12 +14631,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14701,12 +14701,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>46600</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14716,12 +14716,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -14974,12 +14974,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>31137</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44817</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>44097</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15044,12 +15044,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>66662</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>85656</t>
+          <t>85152</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15059,12 +15059,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -15087,12 +15087,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -15200,12 +15200,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28238</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>53365</t>
+          <t>53984</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -15543,12 +15543,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>40666</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15558,12 +15558,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15578,12 +15578,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>52509</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15593,12 +15593,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15613,12 +15613,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>83234</t>
+          <t>84329</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>103895</t>
+          <t>103892</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15628,12 +15628,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -15656,12 +15656,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15691,12 +15691,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15706,12 +15706,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15741,12 +15741,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -15769,12 +15769,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15784,12 +15784,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>16814</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15819,12 +15819,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15839,12 +15839,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54451</t>
+          <t>53321</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>195975</t>
+          <t>194832</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>225812</t>
+          <t>225331</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>190170</t>
+          <t>190288</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>221690</t>
+          <t>222124</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16162,12 +16162,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>392829</t>
+          <t>395099</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>437516</t>
+          <t>437752</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -16225,12 +16225,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16240,12 +16240,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16310,12 +16310,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -16338,12 +16338,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>109721</t>
+          <t>111049</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16373,12 +16373,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>128649</t>
+          <t>127986</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>159801</t>
+          <t>159245</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16388,12 +16388,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16408,12 +16408,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>247456</t>
+          <t>246997</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>290473</t>
+          <t>288664</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16423,12 +16423,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33497</t>
+          <t>33453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -16932,12 +16932,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -16952,12 +16952,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38514</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -16967,12 +16967,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -16987,12 +16987,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>61652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70887</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17100,12 +17100,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17115,12 +17115,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -17143,12 +17143,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -17178,12 +17178,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -17213,12 +17213,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>976</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -17486,12 +17486,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40475</t>
+          <t>40658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17501,12 +17501,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17521,12 +17521,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47954</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>62789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -17536,12 +17536,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17556,12 +17556,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94149</t>
+          <t>91784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115345</t>
+          <t>114572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17571,12 +17571,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -17712,12 +17712,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29073</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -17727,12 +17727,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -17747,12 +17747,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -17762,12 +17762,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -17782,12 +17782,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -17797,12 +17797,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -18055,12 +18055,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -18070,12 +18070,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32899</t>
+          <t>32811</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -18105,12 +18105,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -18125,12 +18125,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66118</t>
+          <t>65492</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18140,12 +18140,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -18281,12 +18281,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -18624,12 +18624,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34054</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41763</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18639,12 +18639,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18659,12 +18659,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53577</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18694,12 +18694,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76418</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93912</t>
+          <t>93343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18709,12 +18709,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -18850,12 +18850,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -18865,12 +18865,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -18885,12 +18885,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -18900,12 +18900,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -18920,12 +18920,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -18935,12 +18935,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -19085,7 +19085,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -19193,12 +19193,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -19228,12 +19228,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>24832</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -19243,12 +19243,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37772</t>
+          <t>38564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -19278,12 +19278,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -19419,12 +19419,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -19434,12 +19434,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -19469,12 +19469,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -19504,12 +19504,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -19762,12 +19762,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -19797,12 +19797,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -19812,12 +19812,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -19832,12 +19832,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39235</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>48469</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -19847,12 +19847,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -19988,12 +19988,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -20003,12 +20003,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -20023,12 +20023,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -20038,12 +20038,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20058,12 +20058,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20073,12 +20073,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -20331,12 +20331,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>68017</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -20346,12 +20346,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -20366,12 +20366,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>72745</t>
+          <t>73305</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>92908</t>
+          <t>93401</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -20381,12 +20381,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>158064</t>
+          <t>158220</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -20416,12 +20416,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20479,12 +20479,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20514,12 +20514,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -20529,12 +20529,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -20557,12 +20557,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20572,12 +20572,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20592,12 +20592,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20607,12 +20607,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20627,12 +20627,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20642,12 +20642,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -20900,12 +20900,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>62629</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>74496</t>
+          <t>74462</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -20915,12 +20915,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -20935,12 +20935,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>72219</t>
+          <t>72720</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>88389</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -20950,12 +20950,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20970,12 +20970,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>140931</t>
+          <t>140539</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>159824</t>
+          <t>159707</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -20985,12 +20985,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -21161,12 +21161,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28050</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -21176,12 +21176,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -21196,12 +21196,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42051</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -21211,12 +21211,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -21356,12 +21356,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -21371,39 +21371,39 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21426,12 +21426,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -21469,12 +21469,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>325163</t>
+          <t>325569</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -21484,12 +21484,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>363788</t>
+          <t>363011</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>400066</t>
+          <t>401364</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21519,12 +21519,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21539,12 +21539,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>675377</t>
+          <t>675793</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>719595</t>
+          <t>719494</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21554,12 +21554,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -21582,12 +21582,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21597,12 +21597,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21617,12 +21617,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21632,12 +21632,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21652,12 +21652,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21667,12 +21667,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -21695,12 +21695,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>60905</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>88060</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21710,12 +21710,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21730,12 +21730,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>111955</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21745,12 +21745,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21765,12 +21765,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>187968</t>
+          <t>186106</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
